--- a/tables/tables performance/all_ap.xlsx
+++ b/tables/tables performance/all_ap.xlsx
@@ -682,52 +682,52 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3146582751203137</v>
+        <v>0.3095206059374356</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3018197393269288</v>
+        <v>0.3428104860895573</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2872766992198196</v>
+        <v>0.2885791458382526</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2610092472424145</v>
+        <v>0.3220472057224573</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3106404882696876</v>
+        <v>0.2973896853541897</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3168569951313866</v>
+        <v>0.3254290503694475</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3073193011283451</v>
+        <v>0.2529046919376007</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3263941021055477</v>
+        <v>0.3341689240081817</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3060270606844065</v>
+        <v>0.2887712874731132</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3314185025728374</v>
+        <v>0.3280268413771049</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2522923887067756</v>
+        <v>0.2305072002454308</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3074622261688348</v>
+        <v>0.3227104133533788</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2878948621550528</v>
+        <v>0.2961640511262374</v>
       </c>
       <c r="O5" t="n">
-        <v>0.269162893571903</v>
+        <v>0.2751671254717879</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2815140777774992</v>
+        <v>0.3093732636313103</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2443094963341608</v>
+        <v>0.2782341918218455</v>
       </c>
     </row>
     <row r="6">
@@ -843,221 +843,221 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>synth_credit_card_fraud_label_AP.csv</t>
+          <t>kdd_AP.csv</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8099146175705969</v>
+        <v>0.0575777387525001</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8751479347255333</v>
+        <v>0.0568344633902143</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7974663484901281</v>
+        <v>0.0585173327698281</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8390469062330571</v>
+        <v>0.0581486143387063</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8045618325634817</v>
+        <v>0.0583993712178612</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8843441953338247</v>
+        <v>0.0584555167927538</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7927362920564776</v>
+        <v>0.0574556037043618</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8710799413584918</v>
+        <v>0.059956857909725</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8021247316397834</v>
+        <v>0.0586490979593633</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8645491844829815</v>
+        <v>0.0573962703332212</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7742570369998265</v>
+        <v>0.0582138372091664</v>
       </c>
       <c r="M8" t="n">
-        <v>0.882999022595065</v>
+        <v>0.0579584948185021</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8223864062932609</v>
+        <v>0.0585900232104054</v>
       </c>
       <c r="O8" t="n">
-        <v>0.844533456549876</v>
+        <v>0.0575344573935529</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7897552900930537</v>
+        <v>0.0585020933402374</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.8420005305157582</v>
+        <v>0.0561727622815867</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>synth_mobile_money_fraud_label_AP.csv</t>
+          <t>synth_credit_card_fraud_label_AP.csv</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5357404212239142</v>
+        <v>0.8099146175705969</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8900586587060793</v>
+        <v>0.8751479347255333</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6780855705918143</v>
+        <v>0.7974663484901281</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8797364906876195</v>
+        <v>0.8390469062330571</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4684283853866111</v>
+        <v>0.8045618325634817</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8780180420880421</v>
+        <v>0.8843441953338247</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3630667753399253</v>
+        <v>0.7927362920564776</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9096476507236052</v>
+        <v>0.8710799413584918</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5178564557926061</v>
+        <v>0.8021247316397834</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8920338713994076</v>
+        <v>0.8645491844829815</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3932176454966677</v>
+        <v>0.7742570369998265</v>
       </c>
       <c r="M9" t="n">
-        <v>0.9070530651672414</v>
+        <v>0.882999022595065</v>
       </c>
       <c r="N9" t="n">
-        <v>0.635400814507469</v>
+        <v>0.8223864062932609</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8860478672220983</v>
+        <v>0.844533456549876</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6507271317956727</v>
+        <v>0.7897552900930537</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.8844662316972079</v>
+        <v>0.8420005305157582</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>telco_customer_churn_AP.csv</t>
+          <t>synth_mobile_money_fraud_label_AP.csv</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1759595521501368</v>
+        <v>0.5357404212239142</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2333980375553606</v>
+        <v>0.8900586587060793</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2263578829242404</v>
+        <v>0.6780855705918143</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1104081998803426</v>
+        <v>0.8797364906876195</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1656572349890245</v>
+        <v>0.4684283853866111</v>
       </c>
       <c r="G10" t="n">
-        <v>0.232256205970479</v>
+        <v>0.8780180420880421</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1877575847435089</v>
+        <v>0.3630667753399253</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2299440279708058</v>
+        <v>0.9096476507236052</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2266828703369569</v>
+        <v>0.5178564557926061</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1495360732213463</v>
+        <v>0.8920338713994076</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1759004216373076</v>
+        <v>0.3932176454966677</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2453750126596796</v>
+        <v>0.9070530651672414</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2262230830214678</v>
+        <v>0.635400814507469</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1412553438354349</v>
+        <v>0.8860478672220983</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2177108685487481</v>
+        <v>0.6507271317956727</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1365418836402717</v>
+        <v>0.8844662316972079</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>ulb_credit_card_fraud_label_AP.csv</t>
+          <t>telco_customer_churn_AP.csv</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.902364634301534</v>
+        <v>0.1759595521501368</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9112509015482484</v>
+        <v>0.2333980375553606</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9158150644870352</v>
+        <v>0.2263578829242404</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9100090530298144</v>
+        <v>0.1104081998803426</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9056374327835039</v>
+        <v>0.1656572349890245</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9145152148414052</v>
+        <v>0.232256205970479</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8971078904763802</v>
+        <v>0.1877575847435089</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9085372936188266</v>
+        <v>0.2299440279708058</v>
       </c>
       <c r="J11" t="n">
-        <v>0.907513665349964</v>
+        <v>0.2266828703369569</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9131956578216772</v>
+        <v>0.1495360732213463</v>
       </c>
       <c r="L11" t="n">
-        <v>0.8882920492980702</v>
+        <v>0.1759004216373076</v>
       </c>
       <c r="M11" t="n">
-        <v>0.9067147977313532</v>
+        <v>0.2453750126596796</v>
       </c>
       <c r="N11" t="n">
-        <v>0.9125233187545472</v>
+        <v>0.2262230830214678</v>
       </c>
       <c r="O11" t="n">
-        <v>0.9143312302990924</v>
+        <v>0.1412553438354349</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9043251043222326</v>
+        <v>0.2177108685487481</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.9147778049174869</v>
+        <v>0.1365418836402717</v>
       </c>
     </row>
     <row r="12">
